--- a/Student_bodies.xlsx
+++ b/Student_bodies.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IIM Amritsar\Tasks\Gradly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6994CDB7-43A5-4108-826C-29C8C5CF510A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D92F4F6-796D-48C0-BB35-35BDF6E33418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="353" windowWidth="21795" windowHeight="13244" xr2:uid="{26D59277-A058-444D-92CB-9CFEB5C1C0A6}"/>
   </bookViews>
@@ -48,66 +48,36 @@
     <t>Alumni Committee </t>
   </si>
   <si>
-    <t>IIM Amritsar, the fastest growing amongst newer IIMs has produced wonderful alumni who are achieving greater heights in the corporate world and are setting the bar high for the upcoming generation. "Nobody is bothered about an institution more than its alumni."- N. R. Narayana Murthy Our alumni follow these wise words in spirit and letter by maintaining a very close relationship with the institute, the depth of which can be corroborated by the existence of Alumni Committee, which has a dedicated team of students leaving no stones unturned to widen the scope for IIM Amritsar alumni interaction. Alumni Committee acting as the interface for interaction between alumni and current students is responsible for organizing alumni-meets and circulating alumni-newsletters. Alumni-meets act as a platform for rejuvenating old bonds and provide an opportunity to current students to learn and gain from alumni's experience.</t>
-  </si>
-  <si>
-    <t>IIM Amritsar believes in the all-round development of students' personalities as the ultimate goal of education. It aims to provide rich cultural experiences that help students appreciate the multi-cultural diversity of our society. The Cultural Committee at IIM Amritsar is the heartbeat of campus life, fostering creativity and camaraderie while also being responsible for the buzz factor during the students' college life. The committee takes care of the social and cultural aspects of life at the institute, ensuring that students have an equal share of fun and entertainment alongside their academic pursuits. It is driven by a team of motivated individuals who provide students with a vibrant platform to explore their passions and showcase their talents.</t>
-  </si>
-  <si>
     <t>Cultural Committee </t>
   </si>
   <si>
     <t>Hostel and Mess Committee</t>
   </si>
   <si>
-    <t>Being away from home is one of the biggest hurdles one will consider before enrolling themselves in a residential programme. For some it is yet another 2 years of hostel life, for others it is their first experience of being all alone by themselves without their family. Home away from home is how we describe our institution. One might miss mom's food but will never remain hungry as a decent mess fills one's tummies with food and one's hearts with warmth.The roles and responsibilities of the committee involves acting as liaisons between the administration and the students. Owing to a wide range of people, the menu is prepared such that the cuisine preference of all students are satisfied. The Hostel and Mess Committee holds the responsibility of keeping a check on the hostel infrastructure, housekeeping issues etc.In short, Hostel and Mess committee makes the hostel life of a student cherishable for a lifetime.</t>
-  </si>
-  <si>
     <t>Industry Interaction Committee </t>
   </si>
   <si>
-    <t>First-hand experience is not the only way how a person can accumulate knowledge about the know-how of the world, the same can be gathered by interacting with people with who possess it already, the knowledge that they have gathered over the years due the time they spent in the industry. This is what precisely Industry Interaction Committee (IIC) tries to do, when they arrange for the speakers, enriched with the experience of corporate corridors, coming down to interact with students. This acts as an opportunity for students as it imparts the knowledge in them about what lies ahead of the degree they are pursuing, what role they may resume in future, and precisely what may be expected out of them on the job as a manager. In a way such interactions give a glimpse of what lies ahead on the road of management studies, and becoming prospective managers. These interactions also provide an opportunity to the students to showcase their acumen by indulging in an engaging Q&amp;A session with the speaker and hence creating the brand value for the institute as a whole. In a broader sense IIC works as the mediator where its role is to connect the future managers with the current one's and provide a platform for active interaction and knowledge sharing for the benefit of all the parties involved.</t>
-  </si>
-  <si>
     <t>Media and Public Relation Committee </t>
   </si>
   <si>
-    <t>Meet MPRC – The Face of IIM Amritsar! The Media and Public Relations Committee (MPRC) is a student-run creative powerhouse, serving as the official spokesperson of IIM Amritsar. It shapes the institute's narrative through strategic communication, media outreach, and comprehensive event coverage, including photography, videography, and live streaming. In addition to maintaining a strong digital and media presence, MPRC enhances IIM Amritsar's Industry Connect Program through conclaves, guest lectures, and workshops while cultivating relationships with corporate partners, media houses, and aspiring students. These initiatives ensure that IIM Amritsar's voice resonates across all platforms. As the bridge between the institute and the world, MPRC engages in press coverage, digital media management, and internal communication, ensuring seamless information flow among students, faculty, and stakeholders. It also collaborates with all student bodies, contributing to every institute event and serving as the archive of IIM Amritsar by documenting its journey. It has a pivotal role in assisting prospective candidates by addressing admission-related queries and offering valuable insights into life at IIM Amritsar. Be it through captivating content, impactful storytelling, or dynamic media collaborations, MPRC is dedicated to amplifying the brand presence of IIM Amritsar.</t>
-  </si>
-  <si>
-    <t>The committee is responsible for interacting with the corporate to create meaningful associations and sponsorship opportunities for them. By leveraging both our academic events like Finance, Marketing, Operations, HR, Strategy conclaves and non-academic events like AArunya (the flagship event of the institute) and Runbhoomi (IIM Amritsar Marathon), the Committee works towards building the brand of the Institute by forging mutually beneficial partnerships with the corporate. The responsibilities of the Committee include fundraising for events, designing mutually beneficial strategies for sponsors and the Institute during events and maintaining long-term relationships with sponsors. The merchandising wing of the committee tries to supplement this core objective of institute brand promotion by procuring merchandise customized to the needs of the students, clubs and committees. Merchandising and Sponsorship committee, MaSCom, thus assists other student bodies and supports the major events throughout the academic year by catering to their merchandising as well as sponsorship needs for creating bigger impact through student activities.</t>
-  </si>
-  <si>
     <t>Merchandising and Sponsorship Committee </t>
   </si>
   <si>
-    <t>The Placement Committee at IIM Amritsar is a student body which is responsible for carrying out all placements related activities. It is an elected body where the members are elected by students of the institute. It consists of a Bi-Cameral framework consisting of senior and junior members. It is a team of highly dedicated students, who work for a common goal of obtaining the desired placement offers for the students in terms of both profiles and organizations to work with. The Placement Committee looks into tasks like student brochure development, resume vetting, pitching, student's skills-job mapping and placement related event organizing. Apart from these tasks, the Placement Committee at IIM Amritsar also conducts mock group discussions, interviews and workshops which equips the students to face the placement interviews and be industry ready. The Placement Committee also plays an important role in developing and sustaining a long term mutually beneficial relationship with the industry.</t>
-  </si>
-  <si>
     <t>Placements' Committee </t>
   </si>
   <si>
     <t>Students' Council </t>
   </si>
   <si>
-    <t>The Students' Council is a students' body whose main purpose is to represent and promote the interests of the students of IIM Amritsar. It acts as the bridge between the faculty, students and the administration serving as the platform of communication to advance academia in the institute. The Students' Council, with the help of the administration, performs its duties to manage and resolve the matters that arise within the students. Approval for creating a new club/committee is jointly taken by the students' council and administration. Any process of dissolution of a committee, impeachment of a member of any committee or amending the constitution is taken in presence of the students' council and the member of the committee concerned. The Students' Council also assists other clubs/ committees in conducting and organizing various co-curricular and extra-curricular activities or events. Students' Council members bring ideas, requests and feedback to the meetings; give students a voice using a democratic process; and make decisions which effects the institution. Students who participate in students' councils, under the supervision of a facilitator or administrator, learn about leadership, problem solving, and teamwork.</t>
-  </si>
-  <si>
     <t>Sports Committee</t>
   </si>
   <si>
-    <t>A dedicated team of passionate individuals committed to promoting and fostering a vibrant sports culture within the college community. Their mission is to provide students with a platform to explore their talents in sports, develop valuable skills, and promote physical fitness and overall well-being. The Sports Committee aims to create an inclusive and supportive environment where students from all backgrounds can participate, compete, and thrive in various sports disciplines. They organize an array of sports events throughout the academic year, including annual sports meets, championships, friendly matches and inter-college events visits. Kritansh, Sangharsh, and Milaap are some of the major events conducted by the committee. These events not only offer a platform for healthy competition but also foster a sense of camaraderie, team spirit, and sportsmanship among participants.</t>
-  </si>
-  <si>
     <t>Body_Type</t>
   </si>
   <si>
     <t>Committee</t>
   </si>
   <si>
-    <t>Increasing amounts of data is being generated at a pace that's hard to fathom and the ability to make sense of such data is of paramount importance for businesses; It helps them derive and act on insights, make better and quick decisions, bring in new or improved products and services and reduce costs. Keeping this in mind, ABC, the analytics and business computing club of IIM Amritsar, seeks to facilitate students' learning and development in data analytics by building an active community of students and faculty that are passionate about data analytics. ABC will act as the premier internal organization for conducting all analytics related events on campus. The club aims to enhance knowledge of business and data analytics by way of knowledge sharing sessions, workshops, quizzes, simulation-based events, case study competitions etc.</t>
-  </si>
-  <si>
     <t>Center of Entrepreneurship </t>
   </si>
   <si>
@@ -123,84 +93,45 @@
     <t>FEC - Finance and Economics Club of IIM Amritsar aims to provide students with an enriching learning experience in the world of Finance by organising numerous interactive events. At FEC, we are passionate about everything from Stock markets and Derivatives to Microfinance and Behavioural Economics.</t>
   </si>
   <si>
-    <t>HRithvi is the club of Human Resources Management at the Indian Institute of Management Amritsar aimed toward the overall development and understanding of the HR domain among management professionals. The club provides a platform for HR enthusiasts to meet, network, share, learn, and implement the best practices, trends, and knowledge. At HRithvi, we are passionate about everything from Talent Acquisition and Performance Management to Employee Well-being and HR Tech.</t>
-  </si>
-  <si>
     <t>HRithvi - The HR Club</t>
   </si>
   <si>
     <t>Invictus Club </t>
   </si>
   <si>
-    <t>Invictus is the premier case competition club of IIM Amritsar, dedicated to equipping students with the skills and strategic thinking necessary to excel in corporate case challenges. Our mission is to create a thriving ecosystem where students can refine their problem-solving abilities, enhance their presentation skills, and gain a competitive edge in national and international case competitions.</t>
-  </si>
-  <si>
     <t>Markophilic - Marketing Club</t>
   </si>
   <si>
-    <t>As turning a blazing spark into an ardent fire is catalysed by its proper fuelling, similarly turning a marketing "philic" into a promising marketing talent is catalysed by the club "Markophilic". The club helps the marketing and sales enthusiasts to amplify and accuminate their skills by providing them with insightful knowledge sessions, apprising events and hands on exposures. The club is equally committed towards the holistic development of the students be it in studies or placements. The various events hosted by the club such as Pariprekshya\'17 (The Marketing Conclave), Mark champ etc., help in keeping the participants conversant with the ongoing trends and developments in the marketing vista. Also, the active presence of the club on social media including various activities such as posting marketing articles every week, highlighting of the ongoing club activities, glorifying the winners of various events etc provide a thorough visibility of the club to the outer world.</t>
-  </si>
-  <si>
     <t>OperaZeal Operations Club</t>
   </si>
   <si>
-    <t>OperaZeal, the operations club of IIM Amritsar is a student run interest group that aims to bridge the gap between academia and industry. It focuses on adding value to the student fraternity at IIM Amritsar by gaining and sharing insights into the best and evolving practices in Operations and Supply Chain domain. OperaZeal is the epicentre for all operations related activities in the campus. We bring all operations enthusiasts to a common ground by exposing them to real-time corporate scenarios and organizing knowledge sharing sessions, group discussions, workshops and industry interaction. The club takes various initiatives to ensure the seamless transfer and gain of knowledge among students.</t>
-  </si>
-  <si>
     <t>50mm - The Photography Club</t>
   </si>
   <si>
-    <t>Photography is a way of feeling, of touching, of loving. What you have caught on films is captured forever. 50mm, The Photography Club of IIM Amritsar is a group of like-minded students who express their love and passion towards photography to seize the moments you want to cherish in your life. Our aim is to capture the vibrancy of IIM life in the campus as well as in the hostel to relish these moments later. Be it a guest lecture, a placement celebration, a birthday or a cultural event, our team is always there to create memories with the camera. The club organizes its annual photography competition "Perspective" where all top-B schools participate to win exciting prizes. The club has prospered and is successful in covering various events of IIM Amritsar whether it is Yukti, Periprekshya, Sankshetra or our own cultural fest - "AArunya". The club has also been involved in organizing various photo walks throughout the year and has also been involved in various workshops to enhance learning and creativity among the students.</t>
-  </si>
-  <si>
     <t>Prep Club</t>
   </si>
   <si>
-    <t>The Prep Club of IIM Amritsar is a student-driven initiative aimed at assisting the students to help them upskill and polish themselves for the better. The club focuses on enlightening the students with the real-time functioning of the industry i.e. bringing them closer to reality and closely working with the individual students for personalized development. The club hosts myriad industry leaders and the brightest minds of leading institutions to share their experiences. As part of customized guidance, the club manages programmes such as the Mentor program, fostering peer to peer learning, etc. Some other initiatives include – workshops on business competitions, how to pick the right certifications, etc. Organizing mock interviews, group discussion sessions, followed by personal feedback sessions and various follow up connects to track the overall progress. The club aims to enable every individual at IIM Amritsar to build themselves as a unique, one-of-a-kind brand!</t>
-  </si>
-  <si>
     <t>Sankalp - Social Service Club</t>
   </si>
   <si>
-    <t>In the era of self-centered thinking when the sense of responsibility towards society and the country is dying out SANKALP is a group that begs to differ. With the motto of "Service to those who serve others" Sankalp provides a platform wherein the budding managers offer their voluntary service in various social initiatives undertaken. Here is a snapshot of a few initiatives taken by the club.</t>
-  </si>
-  <si>
     <t>Stratagem - The Strategy and Consulting Club</t>
   </si>
   <si>
-    <t>The objective of Stratagem—The Strategy and Consulting Club of IIM Amritsar—is to promote the interest in strategy and consulting for the students equip them with pragmatic insights and avant-garde frameworks, the club organizes a diverse array of events, where students can hone their skills by organizing case study and quiz competitions, seminars, and strategy simulation games that simulate the current issues faced by the industry.</t>
-  </si>
-  <si>
     <t>Vaani - The Literary and Public Speaking Club</t>
   </si>
   <si>
-    <t>Vaani, the public speaking and literary club of IIM Amritsar is a platform for students to become effective communicators. Here, students hone their interpersonal skills, enhance time management ability, and mitigate their stage fright. Besides equipping our peers with communication skills, the club also makes sure that they have a knack over literary aspects as well. Vaani actively engages with its audience through means of literary quizzes, speech analysis, and poetries to develop a culture of literature.</t>
-  </si>
-  <si>
     <t>Club</t>
   </si>
   <si>
     <t>Anukriti – The Sustainability and Ethics Cell</t>
   </si>
   <si>
-    <t>At Anukriti, we consider that small daily changes can result in a significant impact in the future. Inspired by the meaning of our name, which translates to "small resemblance," we're dedicated to encouraging students and professionals to adopt sustainable habits in their daily lives. These small, consistent actions can gradually affect larger decisions within an organization, leading to zero carbon emissions.</t>
-  </si>
-  <si>
-    <t>MBA is incomplete without catering to the research acumen of students. IIM Amritsar has launched a first-of-its-kind initiative among IIMs – “Anvesh – The Research Cell.” This body aims to produce high-quality research at national and international levels. It focuses on faculty-mentored student collaborations for research papers and projects. The cell emphasizes making students industry-ready through real-world problem-solving using their academic knowledge.</t>
-  </si>
-  <si>
     <t>Laughter Cell</t>
   </si>
   <si>
-    <t>MBA students are constantly preoccupied with tasks, assignments, and other activities, resulting in stress. The Laughter Cell at IIM Amritsar allows students to forget their stress and immerse themselves in humour. We aim to spread joy, laughter, and smiles. The cell's primary focus is to act as an icebreaker between batches and as a medicine for everyone, not just students.</t>
-  </si>
-  <si>
     <t>Synergy Cell</t>
   </si>
   <si>
-    <t>Synergy is a space dedicated to students' mental health and psychological wellbeing. The Cell aims to help students discover the best version of themselves by truly finding a deep connection between the mind, body, and soul. This interconnectedness helps students build character strength by understanding their values and navigating both professional and personal challenges. Since good leaders are essential to guide society, Synergy also strives to inculcate leadership values in students to shape future communities and organizations.</t>
-  </si>
-  <si>
     <t>Anvesh – The Research Cell</t>
   </si>
   <si>
@@ -280,6 +211,75 @@
   </si>
   <si>
     <t>synergy@iimamritsar.ac.in</t>
+  </si>
+  <si>
+    <t>Recognizing that making sense of data is of paramount importance for businesses, ABC, the analytics club of IIM Amritsar, facilitates student learning in this domain. It builds a passionate community of students and faculty, acting as the premier organization for all on-campus analytics-related workshops, quizzes, and competitions.</t>
+  </si>
+  <si>
+    <t>HRithvi, the Human Resources Management club of IIM Amritsar, aims for the overall development and understanding of the HR domain. It provides a platform for HR enthusiasts to network, share, and learn best practices and trends, covering diverse topics from Talent Acquisition to Employee Well-being and HR Tech.</t>
+  </si>
+  <si>
+    <t>Invictus, the premier case competition club of IIM Amritsar, equips students with the strategic thinking necessary to excel in corporate case challenges. Its mission is to create a thriving ecosystem where students can refine problem-solving abilities, enhance presentation skills, and gain a competitive edge in various competitions.</t>
+  </si>
+  <si>
+    <t>The student run Alumni Committee widens the scope for alumni interaction, acting as an interface between graduates and current students. It is responsible for organizing alumni-meets and circulating newsletters, providing a platform for students to learn and gain valuable insights from their predecessors' corporate experiences.</t>
+  </si>
+  <si>
+    <t>The Cultural Committee, the heartbeat of campus life at IIM Amritsar, fosters creativity and camaraderie. It curates the social and cultural aspects of the institute, ensuring students enjoy entertainment alongside their academic pursuits. It provides a vibrant platform for students to explore their passions and showcase talents.</t>
+  </si>
+  <si>
+    <t>The Hostel and Mess Committee ensures the institution is a "home away from home." Acting as a liaison between students and the administration, it manages hostel infrastructure and prepares a diverse menu to satisfy all. The committee's work makes the residential life of a student cherishable.</t>
+  </si>
+  <si>
+    <t>The Industry Interaction Committee connects future managers with current ones by arranging interactions with experienced corporate speakers. This imparts knowledge on future roles and industry expectations, providing a platform for active knowledge sharing that benefits all parties and builds the institute's brand value.</t>
+  </si>
+  <si>
+    <t>MPRC, the face of IIM Amritsar, is a creative powerhouse and the institute's official spokesperson. It shapes the brand's narrative through strategic communication, media outreach, and comprehensive event coverage, acting as the bridge between the institute and the world to amplify its presence.</t>
+  </si>
+  <si>
+    <t>This committee creates meaningful corporate associations and sponsorship opportunities for academic and non academic events. By forging mutually beneficial partnerships, it builds the institute's brand. Its merchandising wing also procures custom merchandise, supporting the branding and sponsorship needs of other student bodies for their events.</t>
+  </si>
+  <si>
+    <t>The Placement Committee is a student elected body responsible for all placement related activities. This dedicated team works to obtain desired job offers by handling resume vetting, corporate pitching, and organizing mock interviews. It equips students to be industry ready while sustaining long term, mutually beneficial industry relationships.</t>
+  </si>
+  <si>
+    <t>The Students' Council is a student body that represents and promotes the interests of students at IIM Amritsar. It acts as the bridge between students, faculty, and administration, managing student matters and assisting other committees, thereby giving students a voice through a democratic process.</t>
+  </si>
+  <si>
+    <t>The Sports Committee dedicated team is committed to promoting and fostering a vibrant sports culture. Its mission is to provide a platform for students to explore their talents, develop skills, and promote physical well-being. It organizes various events that foster camaraderie, team spirit, and sportsmanship among participants.</t>
+  </si>
+  <si>
+    <t>Markophilic, the marketing club, catalyses promising talent by helping enthusiasts amplify their skills. Through insightful knowledge sessions, hands-on exposures, and major events like marketing conclaves, the club is committed to the holistic development of students, keeping them conversant with the latest industry trends and developments.</t>
+  </si>
+  <si>
+    <t>OperaZeal, the operations club of IIM Amritsar, is a group that aims to bridge the gap between academia and industry. As the epicentre for all operations related activities, it adds value by sharing insights on evolving practices and exposing enthusiasts to real time corporate scenarios.</t>
+  </si>
+  <si>
+    <t>50mm, the Photography Club of IIM Amritsar, comprises like minded students who express their passion by seizing moments to be cherished. The club aims to capture the vibrancy of campus life by covering all events, organizing photo walks, workshops, and its annual inter-B-school photography competition, "Perspective."</t>
+  </si>
+  <si>
+    <t>The Prep Club is a student-driven initiative aimed at upskilling and polishing students for the better. It focuses on personalized development through mentorship programs, workshops, and mock interviews with industry leaders, enabling every individual at IIM Amritsar to build themselves as a unique, one-of-a-kind brand.</t>
+  </si>
+  <si>
+    <t>In an era of self-centered thinking, SANKALP provides a platform for budding managers to serve society. Guided by the motto "Service to those who serve others," the club enables students to volunteer their skills and time for various social initiatives, thereby fostering a sense of responsibility.</t>
+  </si>
+  <si>
+    <t>Stratagem, the Strategy and Consulting Club, aims to promote student interest in these domains. To equip students with pragmatic insights and avant-garde frameworks, the club organizes diverse events like case study competitions and simulation games that help participants hone their strategic skills on current industry issues.</t>
+  </si>
+  <si>
+    <t>Vaani, the public speaking and literary club, is a platform for students to become effective communicators. It helps peers hone interpersonal skills and mitigate stage fright, while also developing their literary knack through quizzes, speech analysis, and poetry to cultivate a culture of literature on campus.</t>
+  </si>
+  <si>
+    <t>Anukriti, inspired by its name meaning "small resemblance," believes small daily changes can create a significant future impact. The club is dedicated to encouraging students and professionals to adopt sustainable habits, believing these consistent actions can influence larger organizational decisions and lead towards zero carbon emissions.</t>
+  </si>
+  <si>
+    <t>Anvesh, the Research Cell, is a first-of-its-kind IIM initiative aiming to produce high-quality research. It focuses on faculty-mentored student collaborations for research papers and projects, emphasizing real-world problem-solving with academic knowledge to make students industry-ready and enhance their research acumen.</t>
+  </si>
+  <si>
+    <t>The Laughter Cell allows students to forget the stress of their preoccupied MBA schedules and immerse themselves in humour. Aiming to spread joy and smiles, the cell's primary focus is to act as an icebreaker between batches and serve as a stress-relieving medicine for the entire community.</t>
+  </si>
+  <si>
+    <t>Synergy is a space dedicated to students' mental health and psychological wellbeing. The cell helps students discover the best version of themselves by fostering a deep connection between mind, body, and soul. This interconnectedness helps build character strength to navigate challenges and inculcate leadership values.</t>
   </si>
 </sst>
 </file>
@@ -353,9 +353,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -682,374 +681,374 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="52.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.59765625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="52.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.59765625" customWidth="1"/>
     <col min="3" max="3" width="21.46484375" customWidth="1"/>
-    <col min="4" max="4" width="255.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="255.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="3" t="s">
+      <c r="C26" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A26" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="D26" t="s">
         <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
